--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,22 +408,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>56.87626</v>
+      </c>
+      <c r="C2">
+        <v>95.04404</v>
+      </c>
+      <c r="D2">
+        <v>83.2625</v>
+      </c>
+      <c r="F2">
         <v>57.25569</v>
       </c>
-      <c r="C2">
-        <v>56.87626</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>100.3227</v>
       </c>
-      <c r="E2">
-        <v>95.04404</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>100.7185</v>
-      </c>
-      <c r="G2">
-        <v>83.2625</v>
       </c>
     </row>
     <row r="3">
@@ -433,28 +433,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>63.28405</v>
+      </c>
+      <c r="C3">
+        <v>96.40392</v>
+      </c>
+      <c r="D3">
+        <v>83.63583</v>
+      </c>
+      <c r="E3">
+        <v>46.10687</v>
+      </c>
+      <c r="F3">
         <v>63.39137</v>
       </c>
-      <c r="C3">
-        <v>63.28405</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>101.8555</v>
       </c>
-      <c r="E3">
-        <v>96.40392</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>102.3757</v>
       </c>
-      <c r="G3">
-        <v>83.63583</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>68.43713</v>
-      </c>
-      <c r="I3">
-        <v>46.10687</v>
       </c>
     </row>
     <row r="4">
@@ -464,28 +464,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>56.97491</v>
+      </c>
+      <c r="C4">
+        <v>96.60621</v>
+      </c>
+      <c r="D4">
+        <v>82.69736</v>
+      </c>
+      <c r="E4">
+        <v>52.94529</v>
+      </c>
+      <c r="F4">
         <v>57.36094</v>
       </c>
-      <c r="C4">
-        <v>56.97491</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>102.0251</v>
       </c>
-      <c r="E4">
-        <v>96.60621</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>100.2827</v>
       </c>
-      <c r="G4">
-        <v>82.69736</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>76.76716999999999</v>
-      </c>
-      <c r="I4">
-        <v>52.94529</v>
       </c>
     </row>
     <row r="5">
@@ -495,28 +495,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>58.08383</v>
+      </c>
+      <c r="C5">
+        <v>94.77612000000001</v>
+      </c>
+      <c r="D5">
+        <v>82.34165</v>
+      </c>
+      <c r="E5">
+        <v>40.49676</v>
+      </c>
+      <c r="F5">
         <v>58.23353</v>
       </c>
-      <c r="C5">
-        <v>58.08383</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>100.5597</v>
       </c>
-      <c r="E5">
-        <v>94.77612000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>100</v>
       </c>
-      <c r="G5">
-        <v>82.34165</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>57.55939</v>
-      </c>
-      <c r="I5">
-        <v>40.49676</v>
       </c>
     </row>
     <row r="6">
@@ -526,28 +526,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>60.11364</v>
+      </c>
+      <c r="C6">
+        <v>97.42071</v>
+      </c>
+      <c r="D6">
+        <v>84.69521</v>
+      </c>
+      <c r="E6">
+        <v>39.23427</v>
+      </c>
+      <c r="F6">
         <v>60.17046</v>
       </c>
-      <c r="C6">
-        <v>60.11364</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>102.9627</v>
       </c>
-      <c r="E6">
-        <v>97.42071</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>101.1025</v>
       </c>
-      <c r="G6">
-        <v>84.69521</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>56.21683</v>
-      </c>
-      <c r="I6">
-        <v>39.23427</v>
       </c>
     </row>
     <row r="7">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>66.34039</v>
+      </c>
+      <c r="C7">
+        <v>96.29383</v>
+      </c>
+      <c r="D7">
+        <v>81.02721</v>
+      </c>
+      <c r="E7">
+        <v>43.23374</v>
+      </c>
+      <c r="F7">
         <v>66.37196</v>
       </c>
-      <c r="C7">
-        <v>66.34039</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>103.6174</v>
       </c>
-      <c r="E7">
-        <v>96.29383</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>106.8992</v>
       </c>
-      <c r="G7">
-        <v>81.02721</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>66.60809</v>
-      </c>
-      <c r="I7">
-        <v>43.23374</v>
       </c>
     </row>
     <row r="8">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>62.59453</v>
+      </c>
+      <c r="C8">
+        <v>95.98915</v>
+      </c>
+      <c r="D8">
+        <v>85.48266</v>
+      </c>
+      <c r="E8">
+        <v>47.72772</v>
+      </c>
+      <c r="F8">
         <v>62.68179</v>
       </c>
-      <c r="C8">
-        <v>62.59453</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>100.7363</v>
       </c>
-      <c r="E8">
-        <v>95.98915</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>103.3937</v>
       </c>
-      <c r="G8">
-        <v>85.48266</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>70.05705</v>
-      </c>
-      <c r="I8">
-        <v>47.72772</v>
       </c>
     </row>
     <row r="9">
@@ -619,28 +619,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>59.18679</v>
+      </c>
+      <c r="C9">
+        <v>95.14794999999999</v>
+      </c>
+      <c r="D9">
+        <v>83.23936</v>
+      </c>
+      <c r="E9">
+        <v>50.56763</v>
+      </c>
+      <c r="F9">
         <v>59.52308</v>
       </c>
-      <c r="C9">
-        <v>59.18679</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>99.86433</v>
       </c>
-      <c r="E9">
-        <v>95.14794999999999</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>100.1666</v>
       </c>
-      <c r="G9">
-        <v>83.23936</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>71.73896999999999</v>
-      </c>
-      <c r="I9">
-        <v>50.56763</v>
       </c>
     </row>
     <row r="10">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>59.70288</v>
+      </c>
+      <c r="C10">
+        <v>96.80851</v>
+      </c>
+      <c r="D10">
+        <v>85.64232</v>
+      </c>
+      <c r="E10">
+        <v>42.42228</v>
+      </c>
+      <c r="F10">
         <v>59.79573</v>
       </c>
-      <c r="C10">
-        <v>59.70288</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>102.5031</v>
       </c>
-      <c r="E10">
-        <v>96.80851</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>100.7557</v>
       </c>
-      <c r="G10">
-        <v>85.64232</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>57.83679</v>
-      </c>
-      <c r="I10">
-        <v>42.42228</v>
       </c>
     </row>
     <row r="11">
@@ -681,28 +681,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>56.63255</v>
+      </c>
+      <c r="C11">
+        <v>95.93942</v>
+      </c>
+      <c r="D11">
+        <v>84.54057</v>
+      </c>
+      <c r="E11">
+        <v>50.51014</v>
+      </c>
+      <c r="F11">
         <v>56.8834</v>
       </c>
-      <c r="C11">
-        <v>56.63255</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.8002</v>
       </c>
-      <c r="E11">
-        <v>95.93942</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>104.4024</v>
       </c>
-      <c r="G11">
-        <v>84.54057</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>75.55797</v>
-      </c>
-      <c r="I11">
-        <v>50.51014</v>
       </c>
     </row>
     <row r="12">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>60.47528</v>
+      </c>
+      <c r="C12">
+        <v>96.62411</v>
+      </c>
+      <c r="D12">
+        <v>89.88727</v>
+      </c>
+      <c r="E12">
+        <v>47.42464</v>
+      </c>
+      <c r="F12">
         <v>60.50259</v>
       </c>
-      <c r="C12">
-        <v>60.47528</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>101.5568</v>
       </c>
-      <c r="E12">
-        <v>96.62411</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>105.7361</v>
       </c>
-      <c r="G12">
-        <v>89.88727</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>69.02670000000001</v>
-      </c>
-      <c r="I12">
-        <v>47.42464</v>
       </c>
     </row>
     <row r="13">
@@ -743,28 +743,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>62.13731</v>
+      </c>
+      <c r="C13">
+        <v>96.1567</v>
+      </c>
+      <c r="D13">
+        <v>85.37130999999999</v>
+      </c>
+      <c r="E13">
+        <v>52.17646</v>
+      </c>
+      <c r="F13">
         <v>62.34343</v>
       </c>
-      <c r="C13">
-        <v>62.13731</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>101.1541</v>
       </c>
-      <c r="E13">
-        <v>96.1567</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>103.7029</v>
       </c>
-      <c r="G13">
-        <v>85.37130999999999</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>80.54850999999999</v>
-      </c>
-      <c r="I13">
-        <v>52.17646</v>
       </c>
     </row>
     <row r="14">
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>61.65599</v>
+      </c>
+      <c r="C14">
+        <v>96.34350999999999</v>
+      </c>
+      <c r="D14">
+        <v>79.7401</v>
+      </c>
+      <c r="E14">
+        <v>36.42987</v>
+      </c>
+      <c r="F14">
         <v>61.80384</v>
       </c>
-      <c r="C14">
-        <v>61.65599</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>104.3945</v>
       </c>
-      <c r="E14">
-        <v>96.34350999999999</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>100.4725</v>
       </c>
-      <c r="G14">
-        <v>79.7401</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>53.91621</v>
-      </c>
-      <c r="I14">
-        <v>36.42987</v>
       </c>
     </row>
     <row r="15">
@@ -805,28 +805,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>68.91994</v>
+      </c>
+      <c r="C15">
+        <v>96.84738</v>
+      </c>
+      <c r="D15">
+        <v>82.89712</v>
+      </c>
+      <c r="E15">
+        <v>46.2578</v>
+      </c>
+      <c r="F15">
         <v>69.67522</v>
       </c>
-      <c r="C15">
-        <v>68.91994</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>102.245</v>
       </c>
-      <c r="E15">
-        <v>96.84738</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>104.1065</v>
       </c>
-      <c r="G15">
-        <v>82.89712</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>68.08732000000001</v>
-      </c>
-      <c r="I15">
-        <v>46.2578</v>
       </c>
     </row>
     <row r="16">
@@ -836,28 +836,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>54.36857</v>
+      </c>
+      <c r="C16">
+        <v>96.34344</v>
+      </c>
+      <c r="D16">
+        <v>80.43096</v>
+      </c>
+      <c r="E16">
+        <v>34.83836</v>
+      </c>
+      <c r="F16">
         <v>54.66226</v>
       </c>
-      <c r="C16">
-        <v>54.36857</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>102.7309</v>
       </c>
-      <c r="E16">
-        <v>96.34344</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>102.8584</v>
       </c>
-      <c r="G16">
-        <v>80.43096</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>49.47903</v>
-      </c>
-      <c r="I16">
-        <v>34.83836</v>
       </c>
     </row>
     <row r="17">
@@ -870,25 +870,25 @@
         <v>55.58252</v>
       </c>
       <c r="C17">
+        <v>96.63251</v>
+      </c>
+      <c r="D17">
+        <v>80.50633000000001</v>
+      </c>
+      <c r="E17">
+        <v>32.30294</v>
+      </c>
+      <c r="F17">
         <v>55.58252</v>
       </c>
-      <c r="D17">
+      <c r="G17">
         <v>103.5139</v>
       </c>
-      <c r="E17">
-        <v>96.63251</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>104.3038</v>
       </c>
-      <c r="G17">
-        <v>80.50633000000001</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>45.74961</v>
-      </c>
-      <c r="I17">
-        <v>32.30294</v>
       </c>
     </row>
     <row r="18">
@@ -898,28 +898,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>61.1276</v>
+      </c>
+      <c r="C18">
+        <v>96.53147</v>
+      </c>
+      <c r="D18">
+        <v>83.63816</v>
+      </c>
+      <c r="E18">
+        <v>43.48481</v>
+      </c>
+      <c r="F18">
         <v>61.21238</v>
       </c>
-      <c r="C18">
-        <v>61.1276</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>102.5734</v>
       </c>
-      <c r="E18">
-        <v>96.53147</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>109.5897</v>
       </c>
-      <c r="G18">
-        <v>83.63816</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>59.00075</v>
-      </c>
-      <c r="I18">
-        <v>43.48481</v>
       </c>
     </row>
     <row r="19">
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>64.97404</v>
+      </c>
+      <c r="C19">
+        <v>97.19081</v>
+      </c>
+      <c r="D19">
+        <v>80.79609000000001</v>
+      </c>
+      <c r="E19">
+        <v>34.97702</v>
+      </c>
+      <c r="F19">
         <v>65.14713999999999</v>
       </c>
-      <c r="C19">
-        <v>64.97404</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>105.5819</v>
       </c>
-      <c r="E19">
-        <v>97.19081</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>100.2095</v>
       </c>
-      <c r="G19">
-        <v>80.79609000000001</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>49.10155</v>
-      </c>
-      <c r="I19">
-        <v>34.97702</v>
       </c>
     </row>
     <row r="20">
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>49.34498</v>
+      </c>
+      <c r="C20">
+        <v>97.12329</v>
+      </c>
+      <c r="D20">
+        <v>81.18949000000001</v>
+      </c>
+      <c r="E20">
+        <v>30.32985</v>
+      </c>
+      <c r="F20">
         <v>49.78166</v>
       </c>
-      <c r="C20">
-        <v>49.34498</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>110</v>
       </c>
-      <c r="E20">
-        <v>97.12329</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>111.3416</v>
       </c>
-      <c r="G20">
-        <v>81.18949000000001</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>40.94932</v>
-      </c>
-      <c r="I20">
-        <v>30.32985</v>
       </c>
     </row>
     <row r="21">
@@ -991,28 +991,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>60.13347</v>
+      </c>
+      <c r="C21">
+        <v>96.52159</v>
+      </c>
+      <c r="D21">
+        <v>83.83076</v>
+      </c>
+      <c r="E21">
+        <v>41.09843</v>
+      </c>
+      <c r="F21">
         <v>60.46391</v>
       </c>
-      <c r="C21">
-        <v>60.13347</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>101.877</v>
       </c>
-      <c r="E21">
-        <v>96.52159</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>99.54903</v>
       </c>
-      <c r="G21">
-        <v>83.83076</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>59.06095</v>
-      </c>
-      <c r="I21">
-        <v>41.09843</v>
       </c>
     </row>
     <row r="22">
@@ -1025,25 +1025,25 @@
         <v>45.5516</v>
       </c>
       <c r="C22">
+        <v>97.16158</v>
+      </c>
+      <c r="D22">
+        <v>84.61539</v>
+      </c>
+      <c r="E22">
+        <v>39.86784</v>
+      </c>
+      <c r="F22">
         <v>45.5516</v>
       </c>
-      <c r="D22">
+      <c r="G22">
         <v>103.9301</v>
       </c>
-      <c r="E22">
-        <v>97.16158</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>95.76922999999999</v>
       </c>
-      <c r="G22">
-        <v>84.61539</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>51.98238</v>
-      </c>
-      <c r="I22">
-        <v>39.86784</v>
       </c>
     </row>
     <row r="23">
@@ -1056,25 +1056,25 @@
         <v>57.6488</v>
       </c>
       <c r="C23">
+        <v>96.67085</v>
+      </c>
+      <c r="D23">
+        <v>83.76067999999999</v>
+      </c>
+      <c r="E23">
+        <v>39.91948</v>
+      </c>
+      <c r="F23">
         <v>57.6488</v>
       </c>
-      <c r="D23">
+      <c r="G23">
         <v>103.2663</v>
       </c>
-      <c r="E23">
-        <v>96.67085</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>102.2222</v>
       </c>
-      <c r="G23">
-        <v>83.76067999999999</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>53.66987</v>
-      </c>
-      <c r="I23">
-        <v>39.91948</v>
       </c>
     </row>
     <row r="24">
@@ -1087,25 +1087,25 @@
         <v>61.37632</v>
       </c>
       <c r="C24">
+        <v>97.56681</v>
+      </c>
+      <c r="D24">
+        <v>85.92856999999999</v>
+      </c>
+      <c r="E24">
+        <v>45.02098</v>
+      </c>
+      <c r="F24">
         <v>61.37632</v>
       </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.872</v>
       </c>
-      <c r="E24">
-        <v>97.56681</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>100.5714</v>
       </c>
-      <c r="G24">
-        <v>85.92856999999999</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>62.686</v>
-      </c>
-      <c r="I24">
-        <v>45.02098</v>
       </c>
     </row>
     <row r="25">
@@ -1118,25 +1118,25 @@
         <v>62.27758</v>
       </c>
       <c r="C25">
+        <v>95.95533</v>
+      </c>
+      <c r="D25">
+        <v>83.27645</v>
+      </c>
+      <c r="E25">
+        <v>33.09729</v>
+      </c>
+      <c r="F25">
         <v>62.27758</v>
       </c>
-      <c r="D25">
+      <c r="G25">
         <v>102.8373</v>
       </c>
-      <c r="E25">
-        <v>95.95533</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>99.71558</v>
       </c>
-      <c r="G25">
-        <v>83.27645</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>45.68966</v>
-      </c>
-      <c r="I25">
-        <v>33.09729</v>
       </c>
     </row>
     <row r="26">
@@ -1146,28 +1146,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>65.05061000000001</v>
+      </c>
+      <c r="C26">
+        <v>97.11864</v>
+      </c>
+      <c r="D26">
+        <v>87.77023</v>
+      </c>
+      <c r="E26">
+        <v>45.16342</v>
+      </c>
+      <c r="F26">
         <v>65.15716999999999</v>
       </c>
-      <c r="C26">
-        <v>65.05061000000001</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>101.6271</v>
       </c>
-      <c r="E26">
-        <v>97.11864</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>99.87645999999999</v>
       </c>
-      <c r="G26">
-        <v>87.77023</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>61.43942</v>
-      </c>
-      <c r="I26">
-        <v>45.16342</v>
       </c>
     </row>
     <row r="27">
@@ -1177,28 +1177,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>58.83101</v>
+      </c>
+      <c r="C27">
+        <v>97.16737999999999</v>
+      </c>
+      <c r="D27">
+        <v>85.85526</v>
+      </c>
+      <c r="E27">
+        <v>33.36283</v>
+      </c>
+      <c r="F27">
         <v>58.95807</v>
       </c>
-      <c r="C27">
-        <v>58.83101</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>104.2918</v>
       </c>
-      <c r="E27">
-        <v>97.16737999999999</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>99.17764</v>
       </c>
-      <c r="G27">
-        <v>85.85526</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>49.73451</v>
-      </c>
-      <c r="I27">
-        <v>33.36283</v>
       </c>
     </row>
     <row r="28">
@@ -1211,25 +1211,25 @@
         <v>60.15625</v>
       </c>
       <c r="C28">
+        <v>98.36956000000001</v>
+      </c>
+      <c r="D28">
+        <v>87.42856999999999</v>
+      </c>
+      <c r="E28">
+        <v>34.61539</v>
+      </c>
+      <c r="F28">
         <v>60.15625</v>
       </c>
-      <c r="D28">
+      <c r="G28">
         <v>103.8043</v>
       </c>
-      <c r="E28">
-        <v>98.36956000000001</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>96</v>
       </c>
-      <c r="G28">
-        <v>87.42856999999999</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>49.74359</v>
-      </c>
-      <c r="I28">
-        <v>34.61539</v>
       </c>
     </row>
     <row r="29">
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>61.80556</v>
+      </c>
+      <c r="C29">
+        <v>96.80956999999999</v>
+      </c>
+      <c r="D29">
+        <v>86.26373</v>
+      </c>
+      <c r="E29">
+        <v>33.16929</v>
+      </c>
+      <c r="F29">
         <v>61.97917</v>
       </c>
-      <c r="C29">
-        <v>61.80556</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>102.7916</v>
       </c>
-      <c r="E29">
-        <v>96.80956999999999</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>98.35165000000001</v>
       </c>
-      <c r="G29">
-        <v>86.26373</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>43.89764</v>
-      </c>
-      <c r="I29">
-        <v>33.16929</v>
       </c>
     </row>
     <row r="30">
@@ -1273,25 +1273,25 @@
         <v>55.6962</v>
       </c>
       <c r="C30">
+        <v>97.95918</v>
+      </c>
+      <c r="D30">
+        <v>75.59808</v>
+      </c>
+      <c r="E30">
+        <v>41.70732</v>
+      </c>
+      <c r="F30">
         <v>55.6962</v>
       </c>
-      <c r="D30">
+      <c r="G30">
         <v>106.3775</v>
       </c>
-      <c r="E30">
-        <v>97.95918</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>95.21531</v>
       </c>
-      <c r="G30">
-        <v>75.59808</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>57.56097</v>
-      </c>
-      <c r="I30">
-        <v>41.70732</v>
       </c>
     </row>
     <row r="31">
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>63.15307</v>
+      </c>
+      <c r="C31">
+        <v>96.1515</v>
+      </c>
+      <c r="D31">
+        <v>85.39193</v>
+      </c>
+      <c r="E31">
+        <v>36.09394</v>
+      </c>
+      <c r="F31">
         <v>63.24473</v>
       </c>
-      <c r="C31">
-        <v>63.15307</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>101.6494</v>
       </c>
-      <c r="E31">
-        <v>96.1515</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>98.81236</v>
       </c>
-      <c r="G31">
-        <v>85.39193</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>51.3597</v>
-      </c>
-      <c r="I31">
-        <v>36.09394</v>
       </c>
     </row>
     <row r="32">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>65.37314000000001</v>
+      </c>
+      <c r="C32">
+        <v>96.64838</v>
+      </c>
+      <c r="D32">
+        <v>85.69794</v>
+      </c>
+      <c r="E32">
+        <v>36.13184</v>
+      </c>
+      <c r="F32">
         <v>65.57214</v>
       </c>
-      <c r="C32">
-        <v>65.37314000000001</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>101.6453</v>
       </c>
-      <c r="E32">
-        <v>96.64838</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>103.7757</v>
       </c>
-      <c r="G32">
-        <v>85.69794</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>52.67413</v>
-      </c>
-      <c r="I32">
-        <v>36.13184</v>
       </c>
     </row>
     <row r="33">
@@ -1363,28 +1363,28 @@
         </is>
       </c>
       <c r="B33">
+        <v>54.10334</v>
+      </c>
+      <c r="C33">
+        <v>96.19313</v>
+      </c>
+      <c r="D33">
+        <v>85.88849999999999</v>
+      </c>
+      <c r="E33">
+        <v>40.0475</v>
+      </c>
+      <c r="F33">
         <v>54.25532</v>
       </c>
-      <c r="C33">
-        <v>54.10334</v>
-      </c>
-      <c r="D33">
+      <c r="G33">
         <v>101.6249</v>
       </c>
-      <c r="E33">
-        <v>96.19313</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>101.5679</v>
       </c>
-      <c r="G33">
-        <v>85.88849999999999</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>55.96199</v>
-      </c>
-      <c r="I33">
-        <v>40.0475</v>
       </c>
     </row>
     <row r="34">
@@ -1394,28 +1394,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>45.25862</v>
+      </c>
+      <c r="C34">
+        <v>98.20246</v>
+      </c>
+      <c r="D34">
+        <v>71.14537</v>
+      </c>
+      <c r="E34">
+        <v>17.65464</v>
+      </c>
+      <c r="F34">
         <v>45.83333</v>
       </c>
-      <c r="C34">
-        <v>45.25862</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>108.0416</v>
       </c>
-      <c r="E34">
-        <v>98.20246</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>90.0881</v>
       </c>
-      <c r="G34">
-        <v>71.14537</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>25.7732</v>
-      </c>
-      <c r="I34">
-        <v>17.65464</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:39</t>
+    <t xml:space="preserve">2026-08-02 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:39</t>
+    <t xml:space="preserve">2026-08-05 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:32</t>
+    <t xml:space="preserve">2026-08-05 18:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:13</t>
+    <t xml:space="preserve">2026-08-16 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:44</t>
+    <t xml:space="preserve">2026-08-19 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:38</t>
+    <t xml:space="preserve">2026-08-28 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:20</t>
+    <t xml:space="preserve">2026-09-06 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
